--- a/sample_data.xlsx
+++ b/sample_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8635707e44139441/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AA22DDA-669E-4AB8-B8CC-8F4EAAE058A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{4AA22DDA-669E-4AB8-B8CC-8F4EAAE058A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2EE5AFB-4F69-43F4-B25A-487220976193}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,12 +26,6 @@
   </si>
   <si>
     <t>Buffer</t>
-  </si>
-  <si>
-    <t>sweat</t>
-  </si>
-  <si>
-    <t>urine</t>
   </si>
   <si>
     <t>Anthracycline</t>
@@ -63,12 +57,20 @@
   <si>
     <t>CCGCGG_7_5_int</t>
   </si>
+  <si>
+    <t>Urine</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sweat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -84,6 +86,11 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -106,9 +113,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -548,22 +556,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>11</v>
-      </c>
-      <c r="F1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -571,7 +579,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>0.1</v>
@@ -594,7 +602,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>0.1</v>
@@ -617,7 +625,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>0.1</v>
@@ -640,7 +648,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -663,7 +671,7 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -686,7 +694,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -709,7 +717,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -732,7 +740,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9">
         <v>10</v>
@@ -755,7 +763,7 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -778,7 +786,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -801,7 +809,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -824,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -847,7 +855,7 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14">
         <v>0.1</v>
@@ -870,7 +878,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C15">
         <v>0.1</v>
@@ -893,7 +901,7 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C16">
         <v>0.1</v>
@@ -916,7 +924,7 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -939,7 +947,7 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -962,7 +970,7 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -985,7 +993,7 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C20">
         <v>10</v>
@@ -1008,7 +1016,7 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C21">
         <v>10</v>
@@ -1031,7 +1039,7 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C22">
         <v>10</v>
@@ -1054,7 +1062,7 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1077,7 +1085,7 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1100,7 +1108,7 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1123,7 +1131,7 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26">
         <v>0.1</v>
@@ -1146,7 +1154,7 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C27">
         <v>0.1</v>
@@ -1169,7 +1177,7 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C28">
         <v>0.1</v>
@@ -1192,7 +1200,7 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -1215,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -1238,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -1261,7 +1269,7 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C32">
         <v>10</v>
@@ -1284,7 +1292,7 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C33">
         <v>10</v>
@@ -1307,7 +1315,7 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C34">
         <v>10</v>
@@ -1330,7 +1338,7 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1353,7 +1361,7 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -1376,7 +1384,7 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1399,7 +1407,7 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C38">
         <v>0.1</v>
@@ -1422,7 +1430,7 @@
         <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C39">
         <v>0.1</v>
@@ -1445,7 +1453,7 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C40">
         <v>0.1</v>
@@ -1468,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C41">
         <v>100</v>
@@ -1491,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C42">
         <v>100</v>
@@ -1514,7 +1522,7 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -1537,7 +1545,7 @@
         <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C44">
         <v>10</v>
@@ -1560,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C45">
         <v>10</v>
@@ -1583,7 +1591,7 @@
         <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C46">
         <v>10</v>
@@ -1606,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -1629,7 +1637,7 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -1652,7 +1660,7 @@
         <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -1675,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C50">
         <v>0.5</v>
@@ -1698,7 +1706,7 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C51">
         <v>0.5</v>
@@ -1721,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C52">
         <v>0.5</v>
@@ -1744,7 +1752,7 @@
         <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C53">
         <v>50</v>
@@ -1767,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C54">
         <v>50</v>
@@ -1790,7 +1798,7 @@
         <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C55">
         <v>50</v>
@@ -1813,7 +1821,7 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C56">
         <v>5</v>
@@ -1836,7 +1844,7 @@
         <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C57">
         <v>5</v>
@@ -1859,7 +1867,7 @@
         <v>1</v>
       </c>
       <c r="B58" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C58">
         <v>5</v>
@@ -1882,7 +1890,7 @@
         <v>1</v>
       </c>
       <c r="B59" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C59">
         <v>0.5</v>
@@ -1905,7 +1913,7 @@
         <v>1</v>
       </c>
       <c r="B60" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C60">
         <v>0.5</v>
@@ -1928,7 +1936,7 @@
         <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C61">
         <v>0.5</v>
@@ -1951,7 +1959,7 @@
         <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C62">
         <v>50</v>
@@ -1974,7 +1982,7 @@
         <v>1</v>
       </c>
       <c r="B63" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C63">
         <v>50</v>
@@ -1997,7 +2005,7 @@
         <v>1</v>
       </c>
       <c r="B64" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C64">
         <v>50</v>
@@ -2020,7 +2028,7 @@
         <v>1</v>
       </c>
       <c r="B65" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C65">
         <v>5</v>
@@ -2043,7 +2051,7 @@
         <v>1</v>
       </c>
       <c r="B66" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C66">
         <v>5</v>
@@ -2066,7 +2074,7 @@
         <v>1</v>
       </c>
       <c r="B67" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C67">
         <v>5</v>
@@ -2089,7 +2097,7 @@
         <v>1</v>
       </c>
       <c r="B68" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C68">
         <v>0.5</v>
@@ -2112,7 +2120,7 @@
         <v>1</v>
       </c>
       <c r="B69" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C69">
         <v>0.5</v>
@@ -2135,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="B70" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C70">
         <v>0.5</v>
@@ -2158,7 +2166,7 @@
         <v>1</v>
       </c>
       <c r="B71" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C71">
         <v>50</v>
@@ -2181,7 +2189,7 @@
         <v>1</v>
       </c>
       <c r="B72" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C72">
         <v>50</v>
@@ -2204,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="B73" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C73">
         <v>50</v>
@@ -2227,7 +2235,7 @@
         <v>1</v>
       </c>
       <c r="B74" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C74">
         <v>5</v>
@@ -2250,7 +2258,7 @@
         <v>1</v>
       </c>
       <c r="B75" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C75">
         <v>5</v>
@@ -2273,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="B76" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C76">
         <v>5</v>
@@ -2296,7 +2304,7 @@
         <v>1</v>
       </c>
       <c r="B77" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C77">
         <v>0.5</v>
@@ -2319,7 +2327,7 @@
         <v>1</v>
       </c>
       <c r="B78" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C78">
         <v>0.5</v>
@@ -2342,7 +2350,7 @@
         <v>1</v>
       </c>
       <c r="B79" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C79">
         <v>0.5</v>
@@ -2365,7 +2373,7 @@
         <v>1</v>
       </c>
       <c r="B80" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C80">
         <v>50</v>
@@ -2388,7 +2396,7 @@
         <v>1</v>
       </c>
       <c r="B81" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C81">
         <v>50</v>
@@ -2411,7 +2419,7 @@
         <v>1</v>
       </c>
       <c r="B82" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C82">
         <v>50</v>
@@ -2434,7 +2442,7 @@
         <v>1</v>
       </c>
       <c r="B83" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C83">
         <v>5</v>
@@ -2457,7 +2465,7 @@
         <v>1</v>
       </c>
       <c r="B84" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C84">
         <v>5</v>
@@ -2480,7 +2488,7 @@
         <v>1</v>
       </c>
       <c r="B85" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C85">
         <v>5</v>
@@ -2499,11 +2507,11 @@
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>2</v>
+      <c r="A86" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -2522,11 +2530,11 @@
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>2</v>
+      <c r="A87" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -2545,11 +2553,11 @@
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>2</v>
+      <c r="A88" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -2568,11 +2576,11 @@
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>2</v>
+      <c r="A89" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C89">
         <v>50</v>
@@ -2591,11 +2599,11 @@
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>2</v>
+      <c r="A90" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C90">
         <v>50</v>
@@ -2614,11 +2622,11 @@
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>2</v>
+      <c r="A91" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C91">
         <v>50</v>
@@ -2637,11 +2645,11 @@
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>2</v>
+      <c r="A92" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -2660,11 +2668,11 @@
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>2</v>
+      <c r="A93" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -2683,11 +2691,11 @@
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>2</v>
+      <c r="A94" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -2706,11 +2714,11 @@
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>2</v>
+      <c r="A95" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C95">
         <v>50</v>
@@ -2729,11 +2737,11 @@
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>2</v>
+      <c r="A96" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C96">
         <v>50</v>
@@ -2752,11 +2760,11 @@
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>2</v>
+      <c r="A97" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C97">
         <v>50</v>
@@ -2775,11 +2783,11 @@
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>2</v>
+      <c r="A98" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -2798,11 +2806,11 @@
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>2</v>
+      <c r="A99" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -2821,11 +2829,11 @@
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>2</v>
+      <c r="A100" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -2844,11 +2852,11 @@
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>2</v>
+      <c r="A101" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C101">
         <v>50</v>
@@ -2867,11 +2875,11 @@
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>2</v>
+      <c r="A102" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B102" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C102">
         <v>50</v>
@@ -2890,11 +2898,11 @@
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>2</v>
+      <c r="A103" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B103" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C103">
         <v>50</v>
@@ -2913,11 +2921,11 @@
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>2</v>
+      <c r="A104" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B104" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -2936,11 +2944,11 @@
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
-        <v>2</v>
+      <c r="A105" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B105" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -2959,11 +2967,11 @@
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>2</v>
+      <c r="A106" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B106" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -2982,11 +2990,11 @@
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>2</v>
+      <c r="A107" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B107" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C107">
         <v>50</v>
@@ -3005,11 +3013,11 @@
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>2</v>
+      <c r="A108" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C108">
         <v>50</v>
@@ -3028,11 +3036,11 @@
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>2</v>
+      <c r="A109" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B109" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C109">
         <v>50</v>
@@ -3051,11 +3059,11 @@
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
+      <c r="A110" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B110" t="s">
         <v>3</v>
-      </c>
-      <c r="B110" t="s">
-        <v>5</v>
       </c>
       <c r="C110">
         <v>1</v>
@@ -3074,11 +3082,11 @@
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
+      <c r="A111" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B111" t="s">
         <v>3</v>
-      </c>
-      <c r="B111" t="s">
-        <v>5</v>
       </c>
       <c r="C111">
         <v>1</v>
@@ -3097,11 +3105,11 @@
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
+      <c r="A112" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B112" t="s">
         <v>3</v>
-      </c>
-      <c r="B112" t="s">
-        <v>5</v>
       </c>
       <c r="C112">
         <v>1</v>
@@ -3120,11 +3128,11 @@
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
+      <c r="A113" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B113" t="s">
         <v>3</v>
-      </c>
-      <c r="B113" t="s">
-        <v>5</v>
       </c>
       <c r="C113">
         <v>50</v>
@@ -3143,11 +3151,11 @@
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
+      <c r="A114" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B114" t="s">
         <v>3</v>
-      </c>
-      <c r="B114" t="s">
-        <v>5</v>
       </c>
       <c r="C114">
         <v>50</v>
@@ -3166,11 +3174,11 @@
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
+      <c r="A115" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B115" t="s">
         <v>3</v>
-      </c>
-      <c r="B115" t="s">
-        <v>5</v>
       </c>
       <c r="C115">
         <v>50</v>
@@ -3189,11 +3197,11 @@
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
-        <v>3</v>
+      <c r="A116" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C116">
         <v>1</v>
@@ -3212,11 +3220,11 @@
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
-        <v>3</v>
+      <c r="A117" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C117">
         <v>1</v>
@@ -3235,11 +3243,11 @@
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
-        <v>3</v>
+      <c r="A118" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C118">
         <v>1</v>
@@ -3258,11 +3266,11 @@
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
-        <v>3</v>
+      <c r="A119" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C119">
         <v>50</v>
@@ -3281,11 +3289,11 @@
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
-        <v>3</v>
+      <c r="A120" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C120">
         <v>50</v>
@@ -3304,11 +3312,11 @@
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
-        <v>3</v>
+      <c r="A121" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C121">
         <v>50</v>
@@ -3327,11 +3335,11 @@
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
-        <v>3</v>
+      <c r="A122" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C122">
         <v>1</v>
@@ -3350,11 +3358,11 @@
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
-        <v>3</v>
+      <c r="A123" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C123">
         <v>1</v>
@@ -3373,11 +3381,11 @@
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
-        <v>3</v>
+      <c r="A124" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C124">
         <v>1</v>
@@ -3396,11 +3404,11 @@
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
-        <v>3</v>
+      <c r="A125" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C125">
         <v>50</v>
@@ -3419,11 +3427,11 @@
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
-        <v>3</v>
+      <c r="A126" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C126">
         <v>50</v>
@@ -3442,11 +3450,11 @@
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
-        <v>3</v>
+      <c r="A127" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B127" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C127">
         <v>50</v>
@@ -3465,11 +3473,11 @@
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
-        <v>3</v>
+      <c r="A128" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B128" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C128">
         <v>1</v>
@@ -3488,11 +3496,11 @@
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
-        <v>3</v>
+      <c r="A129" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B129" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -3511,11 +3519,11 @@
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
-        <v>3</v>
+      <c r="A130" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B130" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -3534,11 +3542,11 @@
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
-        <v>3</v>
+      <c r="A131" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B131" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C131">
         <v>50</v>
@@ -3557,11 +3565,11 @@
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
-        <v>3</v>
+      <c r="A132" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B132" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C132">
         <v>50</v>
@@ -3580,11 +3588,11 @@
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
-        <v>3</v>
+      <c r="A133" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B133" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C133">
         <v>50</v>
